--- a/Studymaterials/生活記録表生徒用_縦型.xlsx
+++ b/Studymaterials/生活記録表生徒用_縦型.xlsx
@@ -8,17 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nakag\Desktop\GitHub\Myownproject\Studymaterials\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{448A5ACA-6A2A-40AE-B89D-BA53BC044819}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{768ADFC3-A792-4567-8124-BDD40A62E4B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="縦型1" sheetId="1" r:id="rId1"/>
-    <sheet name="縦型2" sheetId="2" r:id="rId2"/>
+    <sheet name="縦型日曜始まり" sheetId="1" r:id="rId1"/>
+    <sheet name="縦型月曜始まり" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">縦型1!$A$1:$H$61</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">縦型2!$A$1:$H$61</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">縦型月曜始まり!$A$1:$H$61</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">縦型日曜始まり!$A$1:$H$61</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>

--- a/Studymaterials/生活記録表生徒用_縦型.xlsx
+++ b/Studymaterials/生活記録表生徒用_縦型.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nakag\Desktop\GitHub\Myownproject\Studymaterials\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{768ADFC3-A792-4567-8124-BDD40A62E4B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB645957-5F27-4DC2-8F2D-F4589CBDD4E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="縦型日曜始まり" sheetId="1" r:id="rId1"/>
@@ -26,9 +26,6 @@
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="20">
-  <si>
-    <t>生活記録表（縦型）</t>
-  </si>
   <si>
     <t xml:space="preserve">     日付
 時間</t>
@@ -86,6 +83,10 @@
   </si>
   <si>
     <t>反省点</t>
+  </si>
+  <si>
+    <t>生活記録表</t>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -802,7 +803,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A1" s="28" t="s">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="B1" s="29"/>
       <c r="C1" s="29"/>
@@ -815,33 +816,33 @@
     <row r="2" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="C3" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="D3" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="E3" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="12" t="s">
+      <c r="F3" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="12" t="s">
+      <c r="G3" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="12" t="s">
+      <c r="H3" s="13" t="s">
         <v>7</v>
-      </c>
-      <c r="H3" s="13" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -1381,7 +1382,7 @@
     </row>
     <row r="53" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="14" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B53" s="2"/>
       <c r="C53" s="2"/>
@@ -1393,33 +1394,33 @@
     </row>
     <row r="54" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B54" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B54" s="4" t="s">
-        <v>12</v>
-      </c>
       <c r="C54" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G54" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H54" s="5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="55" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="14" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B55" s="4"/>
       <c r="C55" s="4"/>
@@ -1431,7 +1432,7 @@
     </row>
     <row r="56" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="14" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B56" s="6"/>
       <c r="C56" s="6"/>
@@ -1443,7 +1444,7 @@
     </row>
     <row r="57" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="24" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B57" s="8"/>
       <c r="C57" s="8"/>
@@ -1455,7 +1456,7 @@
     </row>
     <row r="58" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B58" s="8"/>
       <c r="C58" s="8"/>
@@ -1467,7 +1468,7 @@
     </row>
     <row r="59" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B59" s="10"/>
       <c r="C59" s="10"/>
@@ -1479,7 +1480,7 @@
     </row>
     <row r="60" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="25" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B60" s="10"/>
       <c r="C60" s="10"/>
@@ -1491,7 +1492,7 @@
     </row>
     <row r="61" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="14" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B61" s="10"/>
       <c r="C61" s="10"/>
@@ -1526,7 +1527,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A1" s="28" t="s">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="B1" s="29"/>
       <c r="C1" s="29"/>
@@ -1539,33 +1540,33 @@
     <row r="2" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="F3" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="G3" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="H3" s="13" t="s">
         <v>1</v>
-      </c>
-      <c r="B3" s="12" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="12" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="G3" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="H3" s="13" t="s">
-        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -2105,7 +2106,7 @@
     </row>
     <row r="53" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="14" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B53" s="2"/>
       <c r="C53" s="2"/>
@@ -2117,33 +2118,33 @@
     </row>
     <row r="54" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B54" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B54" s="4" t="s">
-        <v>12</v>
-      </c>
       <c r="C54" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G54" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H54" s="5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="55" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="14" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B55" s="4"/>
       <c r="C55" s="4"/>
@@ -2155,7 +2156,7 @@
     </row>
     <row r="56" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="14" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B56" s="6"/>
       <c r="C56" s="6"/>
@@ -2167,7 +2168,7 @@
     </row>
     <row r="57" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="24" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B57" s="8"/>
       <c r="C57" s="8"/>
@@ -2179,7 +2180,7 @@
     </row>
     <row r="58" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B58" s="8"/>
       <c r="C58" s="8"/>
@@ -2191,7 +2192,7 @@
     </row>
     <row r="59" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B59" s="10"/>
       <c r="C59" s="10"/>
@@ -2203,7 +2204,7 @@
     </row>
     <row r="60" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="25" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B60" s="10"/>
       <c r="C60" s="10"/>
@@ -2215,7 +2216,7 @@
     </row>
     <row r="61" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="14" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B61" s="10"/>
       <c r="C61" s="10"/>
